--- a/input/reg_RMSE.xlsx
+++ b/input/reg_RMSE.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>REGRESSOR</t>
   </si>
@@ -33,6 +33,15 @@
     <t>W1mb</t>
   </si>
   <si>
+    <t>I1b</t>
+  </si>
+  <si>
+    <t>I2b</t>
+  </si>
+  <si>
+    <t>I3b</t>
+  </si>
+  <si>
     <t>S2d</t>
   </si>
   <si>
@@ -85,15 +94,6 @@
   </si>
   <si>
     <t>DLS2_Males</t>
-  </si>
-  <si>
-    <t>I1b</t>
-  </si>
-  <si>
-    <t>I2b</t>
-  </si>
-  <si>
-    <t>I3b</t>
   </si>
 </sst>
 </file>
@@ -153,7 +153,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>0.82234275691759162</v>
+        <v>0.81845421244698169</v>
       </c>
     </row>
     <row r="3">
@@ -161,7 +161,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.83792532644113804</v>
+        <v>0.8318231278642283</v>
       </c>
     </row>
     <row r="4">
@@ -169,7 +169,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.5264983792380612</v>
+        <v>0.52842580917125537</v>
       </c>
     </row>
     <row r="5">
@@ -177,36 +177,36 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.63836432332229631</v>
+        <v>0.63796656252519179</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>1.7468995158737433</v>
+        <v>1.7455110656071953</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>0.98317862109172471</v>
+        <v>0.97409509625211432</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>1.1366794769234716</v>
+        <v>1.1379638179668805</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>1.036047441983782</v>
@@ -214,7 +214,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>0.84870070750541715</v>
@@ -222,7 +222,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>1.1484500852818154</v>
@@ -230,7 +230,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>1.1927903832324709</v>
@@ -238,114 +238,114 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B13">
-        <v>4.4657200933944825</v>
+        <v>4.4608727317206842</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B14">
-        <v>4.2454870928700768</v>
+        <v>4.2488100047405588</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B15">
-        <v>3.7334678927716096</v>
+        <v>3.7376343170238648</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B16">
-        <v>2.5968934340152487</v>
+        <v>2.5968664130199306</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B17">
-        <v>2.1850999783221869</v>
+        <v>2.1885543164797094</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B18">
-        <v>7.9740614733831601</v>
+        <v>7.966919324090096</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B19">
-        <v>7.1563489802537514</v>
+        <v>7.1657841258237269</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B20">
-        <v>6.4795870806835127</v>
+        <v>6.4859586641425091</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B21">
-        <v>7.0739971316060766</v>
+        <v>7.0661394726712041</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B22">
-        <v>6.0410451072238409</v>
+        <v>6.0523880929117633</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B23">
-        <v>5.4167304831788856</v>
+        <v>5.4222029042219946</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B24">
-        <v>1.9032797391024161</v>
+        <v>1.902513219539105</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B25">
-        <v>1.7095911017754466</v>
+        <v>1.7134881680118068</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B26">
-        <v>1.6232840041455756</v>
+        <v>1.6261256004830791</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_RMSE.xlsx
+++ b/input/reg_RMSE.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="27">
   <si>
     <t>REGRESSOR</t>
   </si>
@@ -201,7 +201,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>1.1379638179668805</v>
+        <v>1.1371953973690609</v>
       </c>
     </row>
     <row r="9">
